--- a/2026-09-28_Audited_Fiber_Models_Rev2/FWA_n50_Dynamic_Business_Case_Rev2.xlsx
+++ b/2026-09-28_Audited_Fiber_Models_Rev2/FWA_n50_Dynamic_Business_Case_Rev2.xlsx
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="D63" s="76">
-        <f>'ARPU &amp; Breakeven Engine'!H8</f>
+        <f>IFERROR(MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0) - 1 + ABS(INDEX(D57:M57, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)-1)) / INDEX(D56:M56, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)), "Over 10 Years")</f>
         <v/>
       </c>
     </row>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="D63" s="76">
-        <f>'ARPU &amp; Breakeven Engine'!H8</f>
+        <f>IFERROR(MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0) - 1 + ABS(INDEX(D57:M57, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)-1)) / INDEX(D56:M56, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)), "Over 10 Years")</f>
         <v/>
       </c>
     </row>
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="D63" s="76">
-        <f>'ARPU &amp; Breakeven Engine'!H8</f>
+        <f>IFERROR(MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0) - 1 + ABS(INDEX(D57:M57, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)-1)) / INDEX(D56:M56, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)), "Over 10 Years")</f>
         <v/>
       </c>
     </row>
@@ -13920,7 +13920,7 @@
         </is>
       </c>
       <c r="D63" s="76">
-        <f>'ARPU &amp; Breakeven Engine'!H8</f>
+        <f>IFERROR(MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0) - 1 + ABS(INDEX(D57:M57, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)-1)) / INDEX(D56:M56, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)), "Over 10 Years")</f>
         <v/>
       </c>
     </row>
@@ -17044,7 +17044,7 @@
         </is>
       </c>
       <c r="D63" s="76">
-        <f>'ARPU &amp; Breakeven Engine'!H8</f>
+        <f>IFERROR(MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0) - 1 + ABS(INDEX(D57:M57, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)-1)) / INDEX(D56:M56, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)), "Over 10 Years")</f>
         <v/>
       </c>
     </row>
@@ -18081,6 +18081,11 @@
           <t>Viability vs Market Pricing (₱599)</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Simple Payback Period (Yrs)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18113,6 +18118,10 @@
         <f>IF(E6&lt;=599, "HIGHLY VIABLE (@ ₱599)", IF(E6&lt;=699, "VIABLE (@ ₱699)", "CHALLENGING (&gt; ₱700)"))</f>
         <v/>
       </c>
+      <c r="H6">
+        <f>S1_Leased_FOC_NonDef!D63</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18145,6 +18154,10 @@
         <f>IF(E7&lt;=599, "HIGHLY VIABLE (@ ₱599)", IF(E7&lt;=699, "VIABLE (@ ₱699)", "CHALLENGING (&gt; ₱700)"))</f>
         <v/>
       </c>
+      <c r="H7">
+        <f>S2_Leased_FOC_Deferred!D63</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18177,6 +18190,10 @@
         <f>IF(E8&lt;=599, "HIGHLY VIABLE (@ ₱599)", IF(E8&lt;=699, "VIABLE (@ ₱699)", "CHALLENGING (&gt; ₱700)"))</f>
         <v/>
       </c>
+      <c r="H8">
+        <f>S3_Leased_Star_NonDef!D63</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18209,6 +18226,10 @@
         <f>IF(E9&lt;=599, "HIGHLY VIABLE (@ ₱599)", IF(E9&lt;=699, "VIABLE (@ ₱699)", "CHALLENGING (&gt; ₱700)"))</f>
         <v/>
       </c>
+      <c r="H9">
+        <f>S4_Leased_Star_Deferred!D63</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -18241,6 +18262,10 @@
         <f>IF(E10&lt;=599, "HIGHLY VIABLE (@ ₱599)", IF(E10&lt;=699, "VIABLE (@ ₱699)", "CHALLENGING (&gt; ₱700)"))</f>
         <v/>
       </c>
+      <c r="H10">
+        <f>S5_Own_FOC_NonDef!D63</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18273,6 +18298,10 @@
         <f>IF(E11&lt;=599, "HIGHLY VIABLE (@ ₱599)", IF(E11&lt;=699, "VIABLE (@ ₱699)", "CHALLENGING (&gt; ₱700)"))</f>
         <v/>
       </c>
+      <c r="H11">
+        <f>S6_Own_FOC_Deferred!D63</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18305,6 +18334,10 @@
         <f>IF(E12&lt;=599, "HIGHLY VIABLE (@ ₱599)", IF(E12&lt;=699, "VIABLE (@ ₱699)", "CHALLENGING (&gt; ₱700)"))</f>
         <v/>
       </c>
+      <c r="H12">
+        <f>S7_Own_Star_NonDef!D63</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18335,6 +18368,10 @@
       </c>
       <c r="G13">
         <f>IF(E13&lt;=599, "HIGHLY VIABLE (@ ₱599)", IF(E13&lt;=699, "VIABLE (@ ₱699)", "CHALLENGING (&gt; ₱700)"))</f>
+        <v/>
+      </c>
+      <c r="H13">
+        <f>S8_Own_Star_Deferred!D63</f>
         <v/>
       </c>
     </row>
@@ -20771,7 +20808,7 @@
       </c>
       <c r="E46" s="31" t="inlineStr">
         <is>
-          <t>B46: 80,000 kHz x ₱5.00/kHz x 1,000 stations = ₱400,000,000 PHP/year ($7.27M USD)</t>
+          <t>NTC Spectrum Users Fee (SUF): 80 MHz channel in n50 band (80,000 kHz) at NTC mandated rate of ₱5.00/kHz/station across 1,000 baseline stations = 80,000 kHz x ₱5.00 x 1,000 stations = ₱400,000,000 PHP/year ($7.2727M USD/year).</t>
         </is>
       </c>
     </row>
@@ -24470,7 +24507,7 @@
         </is>
       </c>
       <c r="D63" s="76">
-        <f>'ARPU &amp; Breakeven Engine'!H8</f>
+        <f>IFERROR(MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0) - 1 + ABS(INDEX(D57:M57, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)-1)) / INDEX(D56:M56, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)), "Over 10 Years")</f>
         <v/>
       </c>
     </row>
@@ -27584,7 +27621,7 @@
         </is>
       </c>
       <c r="D63" s="76">
-        <f>'ARPU &amp; Breakeven Engine'!H8</f>
+        <f>IFERROR(MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0) - 1 + ABS(INDEX(D57:M57, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)-1)) / INDEX(D56:M56, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)), "Over 10 Years")</f>
         <v/>
       </c>
     </row>
@@ -30677,7 +30714,7 @@
         </is>
       </c>
       <c r="D63" s="76">
-        <f>'ARPU &amp; Breakeven Engine'!H8</f>
+        <f>IFERROR(MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0) - 1 + ABS(INDEX(D57:M57, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)-1)) / INDEX(D56:M56, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)), "Over 10 Years")</f>
         <v/>
       </c>
     </row>
@@ -33801,7 +33838,7 @@
         </is>
       </c>
       <c r="D63" s="76">
-        <f>'ARPU &amp; Breakeven Engine'!H8</f>
+        <f>IFERROR(MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0) - 1 + ABS(INDEX(D57:M57, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)-1)) / INDEX(D56:M56, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)), "Over 10 Years")</f>
         <v/>
       </c>
     </row>
@@ -36904,7 +36941,7 @@
         </is>
       </c>
       <c r="D63" s="76">
-        <f>'ARPU &amp; Breakeven Engine'!H8</f>
+        <f>IFERROR(MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0) - 1 + ABS(INDEX(D57:M57, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)-1)) / INDEX(D56:M56, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)), "Over 10 Years")</f>
         <v/>
       </c>
     </row>
@@ -40038,7 +40075,7 @@
         </is>
       </c>
       <c r="D63" s="76">
-        <f>'ARPU &amp; Breakeven Engine'!H8</f>
+        <f>IFERROR(MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0) - 1 + ABS(INDEX(D57:M57, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)-1)) / INDEX(D56:M56, MATCH(TRUE, INDEX(D57:M57&gt;0, 0), 0)), "Over 10 Years")</f>
         <v/>
       </c>
     </row>

--- a/2026-09-28_Audited_Fiber_Models_Rev2/FWA_n50_Dynamic_Business_Case_Rev2.xlsx
+++ b/2026-09-28_Audited_Fiber_Models_Rev2/FWA_n50_Dynamic_Business_Case_Rev2.xlsx
@@ -963,7 +963,7 @@
         <v/>
       </c>
       <c r="B11" s="13">
-        <f>CONCATENATE('Master Comparison'!B5, ' + ', 'Master Comparison'!C5, ' (', 'Master Comparison'!D5, ')')</f>
+        <f>'Master Comparison'!B5 &amp; " + " &amp; 'Master Comparison'!C5 &amp; " (" &amp; 'Master Comparison'!D5 &amp; ")"</f>
         <v/>
       </c>
       <c r="C11" s="5">
@@ -1009,7 +1009,7 @@
         <v/>
       </c>
       <c r="B12" s="13">
-        <f>CONCATENATE('Master Comparison'!B6, ' + ', 'Master Comparison'!C6, ' (', 'Master Comparison'!D6, ')')</f>
+        <f>'Master Comparison'!B6 &amp; " + " &amp; 'Master Comparison'!C6 &amp; " (" &amp; 'Master Comparison'!D6 &amp; ")"</f>
         <v/>
       </c>
       <c r="C12" s="5">
@@ -1055,7 +1055,7 @@
         <v/>
       </c>
       <c r="B13" s="13">
-        <f>CONCATENATE('Master Comparison'!B7, ' + ', 'Master Comparison'!C7, ' (', 'Master Comparison'!D7, ')')</f>
+        <f>'Master Comparison'!B7 &amp; " + " &amp; 'Master Comparison'!C7 &amp; " (" &amp; 'Master Comparison'!D7 &amp; ")"</f>
         <v/>
       </c>
       <c r="C13" s="5">
@@ -1101,7 +1101,7 @@
         <v/>
       </c>
       <c r="B14" s="13">
-        <f>CONCATENATE('Master Comparison'!B8, ' + ', 'Master Comparison'!C8, ' (', 'Master Comparison'!D8, ')')</f>
+        <f>'Master Comparison'!B8 &amp; " + " &amp; 'Master Comparison'!C8 &amp; " (" &amp; 'Master Comparison'!D8 &amp; ")"</f>
         <v/>
       </c>
       <c r="C14" s="5">
@@ -1147,7 +1147,7 @@
         <v/>
       </c>
       <c r="B15" s="13">
-        <f>CONCATENATE('Master Comparison'!B9, ' + ', 'Master Comparison'!C9, ' (', 'Master Comparison'!D9, ')')</f>
+        <f>'Master Comparison'!B9 &amp; " + " &amp; 'Master Comparison'!C9 &amp; " (" &amp; 'Master Comparison'!D9 &amp; ")"</f>
         <v/>
       </c>
       <c r="C15" s="5">
@@ -1193,7 +1193,7 @@
         <v/>
       </c>
       <c r="B16" s="13">
-        <f>CONCATENATE('Master Comparison'!B10, ' + ', 'Master Comparison'!C10, ' (', 'Master Comparison'!D10, ')')</f>
+        <f>'Master Comparison'!B10 &amp; " + " &amp; 'Master Comparison'!C10 &amp; " (" &amp; 'Master Comparison'!D10 &amp; ")"</f>
         <v/>
       </c>
       <c r="C16" s="5">
@@ -1239,7 +1239,7 @@
         <v/>
       </c>
       <c r="B17" s="13">
-        <f>CONCATENATE('Master Comparison'!B11, ' + ', 'Master Comparison'!C11, ' (', 'Master Comparison'!D11, ')')</f>
+        <f>'Master Comparison'!B11 &amp; " + " &amp; 'Master Comparison'!C11 &amp; " (" &amp; 'Master Comparison'!D11 &amp; ")"</f>
         <v/>
       </c>
       <c r="C17" s="5">
@@ -1285,7 +1285,7 @@
         <v/>
       </c>
       <c r="B18" s="13">
-        <f>CONCATENATE('Master Comparison'!B12, ' + ', 'Master Comparison'!C12, ' (', 'Master Comparison'!D12, ')')</f>
+        <f>'Master Comparison'!B12 &amp; " + " &amp; 'Master Comparison'!C12 &amp; " (" &amp; 'Master Comparison'!D12 &amp; ")"</f>
         <v/>
       </c>
       <c r="C18" s="5">
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="B19" s="20">
-        <f>CONCATENATE('Master Comparison'!B13, ' + ', 'Master Comparison'!C13, ' (', 'Master Comparison'!D13, ')')</f>
+        <f>'Master Comparison'!B13 &amp; " + " &amp; 'Master Comparison'!C13 &amp; " (" &amp; 'Master Comparison'!D13 &amp; ")"</f>
         <v/>
       </c>
       <c r="C19" s="21">
@@ -1377,7 +1377,7 @@
         <v/>
       </c>
       <c r="B20" s="20">
-        <f>CONCATENATE('Master Comparison'!B14, ' + ', 'Master Comparison'!C14, ' (', 'Master Comparison'!D14, ')')</f>
+        <f>'Master Comparison'!B14 &amp; " + " &amp; 'Master Comparison'!C14 &amp; " (" &amp; 'Master Comparison'!D14 &amp; ")"</f>
         <v/>
       </c>
       <c r="C20" s="21">
@@ -1423,7 +1423,7 @@
         <v/>
       </c>
       <c r="B21" s="20">
-        <f>CONCATENATE('Master Comparison'!B15, ' + ', 'Master Comparison'!C15, ' (', 'Master Comparison'!D15, ')')</f>
+        <f>'Master Comparison'!B15 &amp; " + " &amp; 'Master Comparison'!C15 &amp; " (" &amp; 'Master Comparison'!D15 &amp; ")"</f>
         <v/>
       </c>
       <c r="C21" s="21">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>Spectrum User Fees (SUF 80 MHz @ ₱5.00/kHz)</t>
+          <t>Spectrum User Fees (SUF 60 MHz @ ₱5.00/kHz)</t>
         </is>
       </c>
       <c r="C27" s="46" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>Spectrum User Fees (SUF 80 MHz @ ₱5.00/kHz)</t>
+          <t>Spectrum User Fees (SUF 60 MHz @ ₱5.00/kHz)</t>
         </is>
       </c>
       <c r="C27" s="46" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>Spectrum User Fees (SUF 80 MHz @ ₱5.00/kHz)</t>
+          <t>Spectrum User Fees (SUF 60 MHz @ ₱5.00/kHz)</t>
         </is>
       </c>
       <c r="C27" s="46" t="inlineStr">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>Spectrum User Fees (SUF 80 MHz @ ₱5.00/kHz)</t>
+          <t>Spectrum User Fees (SUF 60 MHz @ ₱5.00/kHz)</t>
         </is>
       </c>
       <c r="C27" s="46" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>Spectrum User Fees (SUF 80 MHz @ ₱5.00/kHz)</t>
+          <t>Spectrum User Fees (SUF 60 MHz @ ₱5.00/kHz)</t>
         </is>
       </c>
       <c r="C27" s="46" t="inlineStr">
@@ -17147,7 +17147,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FWA 5G n50 (80 MHz) — Master 11-Scenario Evaluation (Revision 2 Audited)</t>
+          <t>FWA 5G n50 (60 MHz) — Master 11-Scenario Evaluation (Revision 2 Audited)</t>
         </is>
       </c>
     </row>
@@ -18834,7 +18834,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FWA 5G n50 (80 MHz) — Table 3: Strategic Financial Matrix (Revision 2 Audited)</t>
+          <t>FWA 5G n50 (60 MHz) — Table 3: Strategic Financial Matrix (Revision 2 Audited)</t>
         </is>
       </c>
     </row>
@@ -19721,7 +19721,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FWA 5G n50 (80 MHz) — Central Model Assumptions &amp; Levers (Revision 2 Audited)</t>
+          <t>FWA 5G n50 (60 MHz) — Central Model Assumptions &amp; Levers (Revision 2 Audited)</t>
         </is>
       </c>
     </row>
@@ -19930,7 +19930,7 @@
       </c>
       <c r="E11" s="31" t="inlineStr">
         <is>
-          <t>B11: 1,000 additional sites deployed per year (scaling to 10,000 sites)</t>
+          <t>B11: 1,000 additional sites deployed per year across Years 1–5, scaling to 5,000 sites total (remaining steady state in Years 6–10)</t>
         </is>
       </c>
     </row>
@@ -20198,7 +20198,7 @@
         </is>
       </c>
       <c r="C22" s="70" t="n">
-        <v>26000</v>
+        <v>75000</v>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
       </c>
       <c r="E22" s="31" t="inlineStr">
         <is>
-          <t>B22: Price Book F3: 80 MHz n50 3-Sector 8T8R MIMO macro BTS</t>
+          <t>B22: 80 MHz n50 3-Sector 8T8R MIMO macro BTS ($75,000/site)</t>
         </is>
       </c>
     </row>
@@ -20748,7 +20748,7 @@
         </is>
       </c>
       <c r="C44" s="34" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D44" s="30" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
       </c>
       <c r="E44" s="31" t="inlineStr">
         <is>
-          <t>B44: 80 MHz channel in n50 band (80,000 kHz)</t>
+          <t>B44: 60 MHz channel in n50 band (60,000 kHz)</t>
         </is>
       </c>
     </row>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="E46" s="31" t="inlineStr">
         <is>
-          <t>NTC Spectrum Users Fee (SUF): 80 MHz channel in n50 band (80,000 kHz) at NTC mandated rate of ₱5.00/kHz/station across 1,000 baseline stations = 80,000 kHz x ₱5.00 x 1,000 stations = ₱400,000,000 PHP/year ($7.2727M USD/year).</t>
+          <t>NTC Spectrum Users Fee (SUF): 60 MHz channel in n50 band (60,000 kHz) at NTC mandated rate of ₱5.00/kHz/station across 1,000 baseline stations = 60,000 kHz x ₱5.00 x 1,000 stations = ₱300,000,000 PHP/year ($5.4545M USD/year).</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="E47" s="31" t="inlineStr">
         <is>
-          <t>B47: $7,272,727 USD/year unphased across all 10 years</t>
+          <t>B47: $5,454,545 USD/year unphased across all 10 years</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="E53" s="31" t="inlineStr">
         <is>
-          <t>B53: Flat ₱400M/year paid across all years (no phasing)</t>
+          <t>B53: Flat ₱300M/year paid across all years (no phasing)</t>
         </is>
       </c>
     </row>
@@ -22858,7 +22858,7 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>Spectrum User Fees (SUF 80 MHz @ ₱5.00/kHz)</t>
+          <t>Spectrum User Fees (SUF 60 MHz @ ₱5.00/kHz)</t>
         </is>
       </c>
       <c r="C27" s="46" t="inlineStr">
@@ -25941,7 +25941,7 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>Spectrum User Fees (SUF 80 MHz @ ₱5.00/kHz)</t>
+          <t>Spectrum User Fees (SUF 60 MHz @ ₱5.00/kHz)</t>
         </is>
       </c>
       <c r="C27" s="46" t="inlineStr">
@@ -29055,7 +29055,7 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>Spectrum User Fees (SUF 80 MHz @ ₱5.00/kHz)</t>
+          <t>Spectrum User Fees (SUF 60 MHz @ ₱5.00/kHz)</t>
         </is>
       </c>
       <c r="C27" s="46" t="inlineStr">
@@ -32148,7 +32148,7 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>Spectrum User Fees (SUF 80 MHz @ ₱5.00/kHz)</t>
+          <t>Spectrum User Fees (SUF 60 MHz @ ₱5.00/kHz)</t>
         </is>
       </c>
       <c r="C27" s="46" t="inlineStr">
@@ -35282,7 +35282,7 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>Spectrum User Fees (SUF 80 MHz @ ₱5.00/kHz)</t>
+          <t>Spectrum User Fees (SUF 60 MHz @ ₱5.00/kHz)</t>
         </is>
       </c>
       <c r="C27" s="46" t="inlineStr">
@@ -38385,7 +38385,7 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>Spectrum User Fees (SUF 80 MHz @ ₱5.00/kHz)</t>
+          <t>Spectrum User Fees (SUF 60 MHz @ ₱5.00/kHz)</t>
         </is>
       </c>
       <c r="C27" s="46" t="inlineStr">
